--- a/source/5、主管组长管幅异常/主管组长管幅-5月.xlsx
+++ b/source/5、主管组长管幅异常/主管组长管幅-5月.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1001</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1389</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4172" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4460" uniqueCount="96">
   <si>
     <t>数据日期</t>
   </si>
@@ -314,6 +314,12 @@
   </si>
   <si>
     <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1389"/>
+  <dimension ref="A1:H1485"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="12.6363636363636" style="1" customWidth="1"/>
@@ -37367,8 +37373,2504 @@
         <v>19.8</v>
       </c>
     </row>
+    <row r="1390" customHeight="1" spans="1:8">
+      <c r="A1390" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1390" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1390" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1390" s="1">
+        <v>744</v>
+      </c>
+      <c r="E1390" s="1">
+        <v>60</v>
+      </c>
+      <c r="F1390" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1390" s="1">
+        <v>52</v>
+      </c>
+      <c r="H1390" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="1391" customHeight="1" spans="1:8">
+      <c r="A1391" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1391" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1391" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1391" s="1">
+        <v>363</v>
+      </c>
+      <c r="E1391" s="1">
+        <v>29</v>
+      </c>
+      <c r="F1391" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1391" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1391" s="1">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="1392" customHeight="1" spans="1:8">
+      <c r="A1392" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1392" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1392" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1392" s="1">
+        <v>204</v>
+      </c>
+      <c r="E1392" s="1">
+        <v>15</v>
+      </c>
+      <c r="F1392" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1392" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1392" s="1">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="1393" customHeight="1" spans="1:8">
+      <c r="A1393" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1393" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1393" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1393" s="1">
+        <v>562</v>
+      </c>
+      <c r="E1393" s="1">
+        <v>40</v>
+      </c>
+      <c r="F1393" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1393" s="1">
+        <v>33</v>
+      </c>
+      <c r="H1393" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1394" customHeight="1" spans="1:8">
+      <c r="A1394" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1394" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1394" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1394" s="1">
+        <v>282</v>
+      </c>
+      <c r="E1394" s="1">
+        <v>20</v>
+      </c>
+      <c r="F1394" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1394" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1394" s="1">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="1395" customHeight="1" spans="1:8">
+      <c r="A1395" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1395" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1395" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1395" s="1">
+        <v>257</v>
+      </c>
+      <c r="E1395" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1395" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1395" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1395" s="1">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="1396" customHeight="1" spans="1:8">
+      <c r="A1396" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1396" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1396" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1396" s="1">
+        <v>320</v>
+      </c>
+      <c r="E1396" s="1">
+        <v>22</v>
+      </c>
+      <c r="F1396" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1396" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1396" s="1">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="1397" customHeight="1" spans="1:8">
+      <c r="A1397" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1397" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1397" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1397" s="1">
+        <v>387</v>
+      </c>
+      <c r="E1397" s="1">
+        <v>26</v>
+      </c>
+      <c r="F1397" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1397" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1397" s="1">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="1398" customHeight="1" spans="1:8">
+      <c r="A1398" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1398" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1398" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1398" s="1">
+        <v>196</v>
+      </c>
+      <c r="E1398" s="1">
+        <v>13</v>
+      </c>
+      <c r="F1398" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1398" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1398" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1399" customHeight="1" spans="1:8">
+      <c r="A1399" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1399" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1399" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1399" s="1">
+        <v>198</v>
+      </c>
+      <c r="E1399" s="1">
+        <v>13</v>
+      </c>
+      <c r="F1399" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1399" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1399" s="1">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="1400" customHeight="1" spans="1:8">
+      <c r="A1400" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1400" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1400" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1400" s="1">
+        <v>691</v>
+      </c>
+      <c r="E1400" s="1">
+        <v>45</v>
+      </c>
+      <c r="F1400" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1400" s="1">
+        <v>34</v>
+      </c>
+      <c r="H1400" s="1">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="1401" customHeight="1" spans="1:8">
+      <c r="A1401" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1401" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1401" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1401" s="1">
+        <v>322</v>
+      </c>
+      <c r="E1401" s="1">
+        <v>21</v>
+      </c>
+      <c r="F1401" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1401" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1401" s="1">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="1402" customHeight="1" spans="1:8">
+      <c r="A1402" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1402" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1402" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1402" s="1">
+        <v>312</v>
+      </c>
+      <c r="E1402" s="1">
+        <v>20</v>
+      </c>
+      <c r="F1402" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1402" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1402" s="1">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1403" customHeight="1" spans="1:8">
+      <c r="A1403" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1403" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1403" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1403" s="1">
+        <v>375</v>
+      </c>
+      <c r="E1403" s="1">
+        <v>24</v>
+      </c>
+      <c r="F1403" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1403" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1403" s="1">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1404" customHeight="1" spans="1:8">
+      <c r="A1404" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1404" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1404" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1404" s="1">
+        <v>517</v>
+      </c>
+      <c r="E1404" s="1">
+        <v>33</v>
+      </c>
+      <c r="F1404" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1404" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1404" s="1">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1405" customHeight="1" spans="1:8">
+      <c r="A1405" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1405" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1405" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1405" s="1">
+        <v>1575</v>
+      </c>
+      <c r="E1405" s="1">
+        <v>99</v>
+      </c>
+      <c r="F1405" s="1">
+        <v>20</v>
+      </c>
+      <c r="G1405" s="1">
+        <v>79</v>
+      </c>
+      <c r="H1405" s="1">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="1406" customHeight="1" spans="1:8">
+      <c r="A1406" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1406" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1406" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1406" s="1">
+        <v>287</v>
+      </c>
+      <c r="E1406" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1406" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1406" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1406" s="1">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="1407" customHeight="1" spans="1:8">
+      <c r="A1407" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1407" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1407" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1407" s="1">
+        <v>471</v>
+      </c>
+      <c r="E1407" s="1">
+        <v>29</v>
+      </c>
+      <c r="F1407" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1407" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1407" s="1">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="1408" customHeight="1" spans="1:8">
+      <c r="A1408" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1408" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1408" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1408" s="1">
+        <v>1057</v>
+      </c>
+      <c r="E1408" s="1">
+        <v>65</v>
+      </c>
+      <c r="F1408" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1408" s="1">
+        <v>54</v>
+      </c>
+      <c r="H1408" s="1">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="1409" customHeight="1" spans="1:8">
+      <c r="A1409" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1409" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1409" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1409" s="1">
+        <v>990</v>
+      </c>
+      <c r="E1409" s="1">
+        <v>61</v>
+      </c>
+      <c r="F1409" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1409" s="1">
+        <v>56</v>
+      </c>
+      <c r="H1409" s="1">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="1410" customHeight="1" spans="1:8">
+      <c r="A1410" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1410" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1410" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1410" s="1">
+        <v>811</v>
+      </c>
+      <c r="E1410" s="1">
+        <v>49</v>
+      </c>
+      <c r="F1410" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1410" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1410" s="1">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="1411" customHeight="1" spans="1:8">
+      <c r="A1411" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1411" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1411" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1411" s="1">
+        <v>515</v>
+      </c>
+      <c r="E1411" s="1">
+        <v>31</v>
+      </c>
+      <c r="F1411" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1411" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1411" s="1">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="1412" customHeight="1" spans="1:8">
+      <c r="A1412" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1412" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1412" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1412" s="1">
+        <v>467</v>
+      </c>
+      <c r="E1412" s="1">
+        <v>28</v>
+      </c>
+      <c r="F1412" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1412" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1412" s="1">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="1413" customHeight="1" spans="1:8">
+      <c r="A1413" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1413" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1413" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1413" s="1">
+        <v>502</v>
+      </c>
+      <c r="E1413" s="1">
+        <v>30</v>
+      </c>
+      <c r="F1413" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1413" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1413" s="1">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="1414" customHeight="1" spans="1:8">
+      <c r="A1414" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1414" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1414" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1414" s="1">
+        <v>797</v>
+      </c>
+      <c r="E1414" s="1">
+        <v>47</v>
+      </c>
+      <c r="F1414" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1414" s="1">
+        <v>39</v>
+      </c>
+      <c r="H1414" s="1">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="1415" customHeight="1" spans="1:8">
+      <c r="A1415" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1415" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1415" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1415" s="1">
+        <v>529</v>
+      </c>
+      <c r="E1415" s="1">
+        <v>31</v>
+      </c>
+      <c r="F1415" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1415" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1415" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1416" customHeight="1" spans="1:8">
+      <c r="A1416" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1416" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1416" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1416" s="1">
+        <v>1123</v>
+      </c>
+      <c r="E1416" s="1">
+        <v>66</v>
+      </c>
+      <c r="F1416" s="1">
+        <v>14</v>
+      </c>
+      <c r="G1416" s="1">
+        <v>52</v>
+      </c>
+      <c r="H1416" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1417" customHeight="1" spans="1:8">
+      <c r="A1417" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1417" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1417" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1417" s="1">
+        <v>1013</v>
+      </c>
+      <c r="E1417" s="1">
+        <v>58</v>
+      </c>
+      <c r="F1417" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1417" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1417" s="1">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="1418" customHeight="1" spans="1:8">
+      <c r="A1418" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1418" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1418" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1418" s="1">
+        <v>489</v>
+      </c>
+      <c r="E1418" s="1">
+        <v>28</v>
+      </c>
+      <c r="F1418" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1418" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1418" s="1">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="1419" customHeight="1" spans="1:8">
+      <c r="A1419" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1419" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1419" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1419" s="1">
+        <v>653</v>
+      </c>
+      <c r="E1419" s="1">
+        <v>37</v>
+      </c>
+      <c r="F1419" s="1">
+        <v>10</v>
+      </c>
+      <c r="G1419" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1419" s="1">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="1420" customHeight="1" spans="1:8">
+      <c r="A1420" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1420" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1420" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1420" s="1">
+        <v>447</v>
+      </c>
+      <c r="E1420" s="1">
+        <v>25</v>
+      </c>
+      <c r="F1420" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1420" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1420" s="1">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="1421" customHeight="1" spans="1:8">
+      <c r="A1421" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1421" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1421" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1421" s="1">
+        <v>394</v>
+      </c>
+      <c r="E1421" s="1">
+        <v>22</v>
+      </c>
+      <c r="F1421" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1421" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1421" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1422" customHeight="1" spans="1:8">
+      <c r="A1422" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1422" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1422" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1422" s="1">
+        <v>628</v>
+      </c>
+      <c r="E1422" s="1">
+        <v>35</v>
+      </c>
+      <c r="F1422" s="1">
+        <v>9</v>
+      </c>
+      <c r="G1422" s="1">
+        <v>26</v>
+      </c>
+      <c r="H1422" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1423" customHeight="1" spans="1:8">
+      <c r="A1423" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1423" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1423" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1423" s="1">
+        <v>269</v>
+      </c>
+      <c r="E1423" s="1">
+        <v>15</v>
+      </c>
+      <c r="F1423" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1423" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1423" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1424" customHeight="1" spans="1:8">
+      <c r="A1424" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1424" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1424" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1424" s="1">
+        <v>885</v>
+      </c>
+      <c r="E1424" s="1">
+        <v>49</v>
+      </c>
+      <c r="F1424" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1424" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1424" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1425" customHeight="1" spans="1:8">
+      <c r="A1425" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1425" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1425" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1425" s="1">
+        <v>1098</v>
+      </c>
+      <c r="E1425" s="1">
+        <v>60</v>
+      </c>
+      <c r="F1425" s="1">
+        <v>13</v>
+      </c>
+      <c r="G1425" s="1">
+        <v>47</v>
+      </c>
+      <c r="H1425" s="1">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="1426" customHeight="1" spans="1:8">
+      <c r="A1426" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1426" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1426" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1426" s="1">
+        <v>1131</v>
+      </c>
+      <c r="E1426" s="1">
+        <v>61</v>
+      </c>
+      <c r="F1426" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1426" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1426" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="1427" customHeight="1" spans="1:8">
+      <c r="A1427" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1427" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1427" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1427" s="1">
+        <v>951</v>
+      </c>
+      <c r="E1427" s="1">
+        <v>51</v>
+      </c>
+      <c r="F1427" s="1">
+        <v>10</v>
+      </c>
+      <c r="G1427" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1427" s="1">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="1428" customHeight="1" spans="1:8">
+      <c r="A1428" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1428" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1428" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1428" s="1">
+        <v>337</v>
+      </c>
+      <c r="E1428" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1428" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1428" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1428" s="1">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="1429" customHeight="1" spans="1:8">
+      <c r="A1429" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1429" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1429" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1429" s="1">
+        <v>506</v>
+      </c>
+      <c r="E1429" s="1">
+        <v>27</v>
+      </c>
+      <c r="F1429" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1429" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1429" s="1">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="1430" customHeight="1" spans="1:8">
+      <c r="A1430" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1430" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1430" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1430" s="1">
+        <v>818</v>
+      </c>
+      <c r="E1430" s="1">
+        <v>43</v>
+      </c>
+      <c r="F1430" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1430" s="1">
+        <v>32</v>
+      </c>
+      <c r="H1430" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1431" customHeight="1" spans="1:8">
+      <c r="A1431" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1431" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1431" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1431" s="1">
+        <v>1162</v>
+      </c>
+      <c r="E1431" s="1">
+        <v>61</v>
+      </c>
+      <c r="F1431" s="1">
+        <v>12</v>
+      </c>
+      <c r="G1431" s="1">
+        <v>49</v>
+      </c>
+      <c r="H1431" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1432" customHeight="1" spans="1:8">
+      <c r="A1432" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1432" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1432" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1432" s="1">
+        <v>344</v>
+      </c>
+      <c r="E1432" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1432" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1432" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1432" s="1">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="1433" customHeight="1" spans="1:8">
+      <c r="A1433" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1433" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1433" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1433" s="1">
+        <v>1013</v>
+      </c>
+      <c r="E1433" s="1">
+        <v>53</v>
+      </c>
+      <c r="F1433" s="1">
+        <v>10</v>
+      </c>
+      <c r="G1433" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1433" s="1">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="1434" customHeight="1" spans="1:8">
+      <c r="A1434" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1434" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1434" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1434" s="1">
+        <v>1098</v>
+      </c>
+      <c r="E1434" s="1">
+        <v>57</v>
+      </c>
+      <c r="F1434" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1434" s="1">
+        <v>46</v>
+      </c>
+      <c r="H1434" s="1">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="1435" customHeight="1" spans="1:8">
+      <c r="A1435" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1435" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1435" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1435" s="1">
+        <v>522</v>
+      </c>
+      <c r="E1435" s="1">
+        <v>27</v>
+      </c>
+      <c r="F1435" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1435" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1435" s="1">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="1436" customHeight="1" spans="1:8">
+      <c r="A1436" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1436" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1436" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1436" s="1">
+        <v>330</v>
+      </c>
+      <c r="E1436" s="1">
+        <v>17</v>
+      </c>
+      <c r="F1436" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1436" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1436" s="1">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="1437" customHeight="1" spans="1:8">
+      <c r="A1437" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1437" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1437" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1437" s="1">
+        <v>257</v>
+      </c>
+      <c r="E1437" s="1">
+        <v>13</v>
+      </c>
+      <c r="F1437" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1437" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1437" s="1">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="1438" customHeight="1" spans="1:8">
+      <c r="A1438" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1438" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1438" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1438" s="1">
+        <v>362</v>
+      </c>
+      <c r="E1438" s="1">
+        <v>29</v>
+      </c>
+      <c r="F1438" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1438" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1438" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="1439" customHeight="1" spans="1:8">
+      <c r="A1439" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1439" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1439" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1439" s="1">
+        <v>744</v>
+      </c>
+      <c r="E1439" s="1">
+        <v>60</v>
+      </c>
+      <c r="F1439" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1439" s="1">
+        <v>52</v>
+      </c>
+      <c r="H1439" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="1440" customHeight="1" spans="1:8">
+      <c r="A1440" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1440" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1440" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1440" s="1">
+        <v>206</v>
+      </c>
+      <c r="E1440" s="1">
+        <v>15</v>
+      </c>
+      <c r="F1440" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1440" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1440" s="1">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="1441" customHeight="1" spans="1:8">
+      <c r="A1441" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1441" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1441" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1441" s="1">
+        <v>563</v>
+      </c>
+      <c r="E1441" s="1">
+        <v>40</v>
+      </c>
+      <c r="F1441" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1441" s="1">
+        <v>33</v>
+      </c>
+      <c r="H1441" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1442" customHeight="1" spans="1:8">
+      <c r="A1442" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1442" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1442" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1442" s="1">
+        <v>283</v>
+      </c>
+      <c r="E1442" s="1">
+        <v>20</v>
+      </c>
+      <c r="F1442" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1442" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1442" s="1">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="1443" customHeight="1" spans="1:8">
+      <c r="A1443" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1443" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1443" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1443" s="1">
+        <v>257</v>
+      </c>
+      <c r="E1443" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1443" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1443" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1443" s="1">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="1444" customHeight="1" spans="1:8">
+      <c r="A1444" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1444" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1444" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1444" s="1">
+        <v>320</v>
+      </c>
+      <c r="E1444" s="1">
+        <v>22</v>
+      </c>
+      <c r="F1444" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1444" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1444" s="1">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="1445" customHeight="1" spans="1:8">
+      <c r="A1445" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1445" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1445" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1445" s="1">
+        <v>387</v>
+      </c>
+      <c r="E1445" s="1">
+        <v>26</v>
+      </c>
+      <c r="F1445" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1445" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1445" s="1">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="1446" customHeight="1" spans="1:8">
+      <c r="A1446" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1446" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1446" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1446" s="1">
+        <v>196</v>
+      </c>
+      <c r="E1446" s="1">
+        <v>13</v>
+      </c>
+      <c r="F1446" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1446" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1446" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1447" customHeight="1" spans="1:8">
+      <c r="A1447" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1447" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1447" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1447" s="1">
+        <v>197</v>
+      </c>
+      <c r="E1447" s="1">
+        <v>13</v>
+      </c>
+      <c r="F1447" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1447" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1447" s="1">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="1448" customHeight="1" spans="1:8">
+      <c r="A1448" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1448" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1448" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1448" s="1">
+        <v>691</v>
+      </c>
+      <c r="E1448" s="1">
+        <v>45</v>
+      </c>
+      <c r="F1448" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1448" s="1">
+        <v>34</v>
+      </c>
+      <c r="H1448" s="1">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="1449" customHeight="1" spans="1:8">
+      <c r="A1449" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1449" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1449" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1449" s="1">
+        <v>322</v>
+      </c>
+      <c r="E1449" s="1">
+        <v>21</v>
+      </c>
+      <c r="F1449" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1449" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1449" s="1">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="1450" customHeight="1" spans="1:8">
+      <c r="A1450" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1450" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1450" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1450" s="1">
+        <v>514</v>
+      </c>
+      <c r="E1450" s="1">
+        <v>33</v>
+      </c>
+      <c r="F1450" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1450" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1450" s="1">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="1451" customHeight="1" spans="1:8">
+      <c r="A1451" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1451" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1451" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1451" s="1">
+        <v>312</v>
+      </c>
+      <c r="E1451" s="1">
+        <v>20</v>
+      </c>
+      <c r="F1451" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1451" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1451" s="1">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1452" customHeight="1" spans="1:8">
+      <c r="A1452" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1452" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1452" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1452" s="1">
+        <v>375</v>
+      </c>
+      <c r="E1452" s="1">
+        <v>24</v>
+      </c>
+      <c r="F1452" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1452" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1452" s="1">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1453" customHeight="1" spans="1:8">
+      <c r="A1453" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1453" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1453" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1453" s="1">
+        <v>1575</v>
+      </c>
+      <c r="E1453" s="1">
+        <v>99</v>
+      </c>
+      <c r="F1453" s="1">
+        <v>20</v>
+      </c>
+      <c r="G1453" s="1">
+        <v>79</v>
+      </c>
+      <c r="H1453" s="1">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="1454" customHeight="1" spans="1:8">
+      <c r="A1454" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1454" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1454" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1454" s="1">
+        <v>287</v>
+      </c>
+      <c r="E1454" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1454" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1454" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1454" s="1">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="1455" customHeight="1" spans="1:8">
+      <c r="A1455" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1455" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1455" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1455" s="1">
+        <v>985</v>
+      </c>
+      <c r="E1455" s="1">
+        <v>61</v>
+      </c>
+      <c r="F1455" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1455" s="1">
+        <v>56</v>
+      </c>
+      <c r="H1455" s="1">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="1456" customHeight="1" spans="1:8">
+      <c r="A1456" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1456" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1456" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1456" s="1">
+        <v>471</v>
+      </c>
+      <c r="E1456" s="1">
+        <v>29</v>
+      </c>
+      <c r="F1456" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1456" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1456" s="1">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="1457" customHeight="1" spans="1:8">
+      <c r="A1457" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1457" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1457" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1457" s="1">
+        <v>1060</v>
+      </c>
+      <c r="E1457" s="1">
+        <v>65</v>
+      </c>
+      <c r="F1457" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1457" s="1">
+        <v>54</v>
+      </c>
+      <c r="H1457" s="1">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="1458" customHeight="1" spans="1:8">
+      <c r="A1458" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1458" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1458" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1458" s="1">
+        <v>813</v>
+      </c>
+      <c r="E1458" s="1">
+        <v>49</v>
+      </c>
+      <c r="F1458" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1458" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1458" s="1">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="1459" customHeight="1" spans="1:8">
+      <c r="A1459" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1459" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1459" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1459" s="1">
+        <v>514</v>
+      </c>
+      <c r="E1459" s="1">
+        <v>31</v>
+      </c>
+      <c r="F1459" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1459" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1459" s="1">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="1460" customHeight="1" spans="1:8">
+      <c r="A1460" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1460" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1460" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1460" s="1">
+        <v>497</v>
+      </c>
+      <c r="E1460" s="1">
+        <v>30</v>
+      </c>
+      <c r="F1460" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1460" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1460" s="1">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="1461" customHeight="1" spans="1:8">
+      <c r="A1461" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1461" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1461" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1461" s="1">
+        <v>467</v>
+      </c>
+      <c r="E1461" s="1">
+        <v>28</v>
+      </c>
+      <c r="F1461" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1461" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1461" s="1">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="1462" customHeight="1" spans="1:8">
+      <c r="A1462" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1462" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1462" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1462" s="1">
+        <v>797</v>
+      </c>
+      <c r="E1462" s="1">
+        <v>47</v>
+      </c>
+      <c r="F1462" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1462" s="1">
+        <v>39</v>
+      </c>
+      <c r="H1462" s="1">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="1463" customHeight="1" spans="1:8">
+      <c r="A1463" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1463" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1463" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1463" s="1">
+        <v>529</v>
+      </c>
+      <c r="E1463" s="1">
+        <v>31</v>
+      </c>
+      <c r="F1463" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1463" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1463" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1464" customHeight="1" spans="1:8">
+      <c r="A1464" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1464" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1464" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1464" s="1">
+        <v>1124</v>
+      </c>
+      <c r="E1464" s="1">
+        <v>65</v>
+      </c>
+      <c r="F1464" s="1">
+        <v>14</v>
+      </c>
+      <c r="G1464" s="1">
+        <v>51</v>
+      </c>
+      <c r="H1464" s="1">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="1465" customHeight="1" spans="1:8">
+      <c r="A1465" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1465" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1465" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1465" s="1">
+        <v>1013</v>
+      </c>
+      <c r="E1465" s="1">
+        <v>58</v>
+      </c>
+      <c r="F1465" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1465" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1465" s="1">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="1466" customHeight="1" spans="1:8">
+      <c r="A1466" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1466" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1466" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1466" s="1">
+        <v>489</v>
+      </c>
+      <c r="E1466" s="1">
+        <v>28</v>
+      </c>
+      <c r="F1466" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1466" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1466" s="1">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="1467" customHeight="1" spans="1:8">
+      <c r="A1467" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1467" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1467" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1467" s="1">
+        <v>653</v>
+      </c>
+      <c r="E1467" s="1">
+        <v>37</v>
+      </c>
+      <c r="F1467" s="1">
+        <v>10</v>
+      </c>
+      <c r="G1467" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1467" s="1">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="1468" customHeight="1" spans="1:8">
+      <c r="A1468" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1468" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1468" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1468" s="1">
+        <v>394</v>
+      </c>
+      <c r="E1468" s="1">
+        <v>22</v>
+      </c>
+      <c r="F1468" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1468" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1468" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1469" customHeight="1" spans="1:8">
+      <c r="A1469" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1469" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1469" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1469" s="1">
+        <v>628</v>
+      </c>
+      <c r="E1469" s="1">
+        <v>35</v>
+      </c>
+      <c r="F1469" s="1">
+        <v>9</v>
+      </c>
+      <c r="G1469" s="1">
+        <v>26</v>
+      </c>
+      <c r="H1469" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1470" customHeight="1" spans="1:8">
+      <c r="A1470" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1470" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1470" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1470" s="1">
+        <v>269</v>
+      </c>
+      <c r="E1470" s="1">
+        <v>15</v>
+      </c>
+      <c r="F1470" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1470" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1470" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1471" customHeight="1" spans="1:8">
+      <c r="A1471" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1471" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1471" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1471" s="1">
+        <v>449</v>
+      </c>
+      <c r="E1471" s="1">
+        <v>25</v>
+      </c>
+      <c r="F1471" s="1">
+        <v>7</v>
+      </c>
+      <c r="G1471" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1471" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="1472" customHeight="1" spans="1:8">
+      <c r="A1472" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1472" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1472" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1472" s="1">
+        <v>887</v>
+      </c>
+      <c r="E1472" s="1">
+        <v>49</v>
+      </c>
+      <c r="F1472" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1472" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1472" s="1">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="1473" customHeight="1" spans="1:8">
+      <c r="A1473" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1473" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1473" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1473" s="1">
+        <v>1098</v>
+      </c>
+      <c r="E1473" s="1">
+        <v>60</v>
+      </c>
+      <c r="F1473" s="1">
+        <v>13</v>
+      </c>
+      <c r="G1473" s="1">
+        <v>47</v>
+      </c>
+      <c r="H1473" s="1">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="1474" customHeight="1" spans="1:8">
+      <c r="A1474" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1474" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1474" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1474" s="1">
+        <v>1131</v>
+      </c>
+      <c r="E1474" s="1">
+        <v>61</v>
+      </c>
+      <c r="F1474" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1474" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1474" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="1475" customHeight="1" spans="1:8">
+      <c r="A1475" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1475" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1475" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1475" s="1">
+        <v>952</v>
+      </c>
+      <c r="E1475" s="1">
+        <v>51</v>
+      </c>
+      <c r="F1475" s="1">
+        <v>10</v>
+      </c>
+      <c r="G1475" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1475" s="1">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="1476" customHeight="1" spans="1:8">
+      <c r="A1476" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1476" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1476" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1476" s="1">
+        <v>335</v>
+      </c>
+      <c r="E1476" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1476" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1476" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1476" s="1">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="1477" customHeight="1" spans="1:8">
+      <c r="A1477" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1477" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1477" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1477" s="1">
+        <v>506</v>
+      </c>
+      <c r="E1477" s="1">
+        <v>27</v>
+      </c>
+      <c r="F1477" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1477" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1477" s="1">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="1478" customHeight="1" spans="1:8">
+      <c r="A1478" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1478" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1478" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1478" s="1">
+        <v>817</v>
+      </c>
+      <c r="E1478" s="1">
+        <v>43</v>
+      </c>
+      <c r="F1478" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1478" s="1">
+        <v>32</v>
+      </c>
+      <c r="H1478" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1479" customHeight="1" spans="1:8">
+      <c r="A1479" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1479" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1479" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1479" s="1">
+        <v>1162</v>
+      </c>
+      <c r="E1479" s="1">
+        <v>61</v>
+      </c>
+      <c r="F1479" s="1">
+        <v>12</v>
+      </c>
+      <c r="G1479" s="1">
+        <v>49</v>
+      </c>
+      <c r="H1479" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1480" customHeight="1" spans="1:8">
+      <c r="A1480" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1480" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1480" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1480" s="1">
+        <v>1014</v>
+      </c>
+      <c r="E1480" s="1">
+        <v>53</v>
+      </c>
+      <c r="F1480" s="1">
+        <v>10</v>
+      </c>
+      <c r="G1480" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1480" s="1">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="1481" customHeight="1" spans="1:8">
+      <c r="A1481" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1481" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1481" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1481" s="1">
+        <v>346</v>
+      </c>
+      <c r="E1481" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1481" s="1">
+        <v>8</v>
+      </c>
+      <c r="G1481" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1481" s="1">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="1482" customHeight="1" spans="1:8">
+      <c r="A1482" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1482" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1482" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1482" s="1">
+        <v>1097</v>
+      </c>
+      <c r="E1482" s="1">
+        <v>57</v>
+      </c>
+      <c r="F1482" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1482" s="1">
+        <v>46</v>
+      </c>
+      <c r="H1482" s="1">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="1483" customHeight="1" spans="1:8">
+      <c r="A1483" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1483" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1483" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1483" s="1">
+        <v>522</v>
+      </c>
+      <c r="E1483" s="1">
+        <v>27</v>
+      </c>
+      <c r="F1483" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1483" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1483" s="1">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="1484" customHeight="1" spans="1:8">
+      <c r="A1484" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1484" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1484" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1484" s="1">
+        <v>330</v>
+      </c>
+      <c r="E1484" s="1">
+        <v>17</v>
+      </c>
+      <c r="F1484" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1484" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1484" s="1">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="1485" customHeight="1" spans="1:8">
+      <c r="A1485" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1485" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1485" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1485" s="1">
+        <v>256</v>
+      </c>
+      <c r="E1485" s="1">
+        <v>13</v>
+      </c>
+      <c r="F1485" s="1">
+        <v>3</v>
+      </c>
+      <c r="G1485" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1485" s="1">
+        <v>19.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1001" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1389" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
